--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236576</v>
+        <v>123236575</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596739</v>
+        <v>596821</v>
       </c>
       <c r="R2" t="n">
-        <v>6681388</v>
+        <v>6681191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236575</v>
+        <v>123236573</v>
       </c>
       <c r="B3" t="n">
         <v>97319</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596821</v>
+        <v>596831</v>
       </c>
       <c r="R3" t="n">
-        <v>6681191</v>
+        <v>6681167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236581</v>
+        <v>123236577</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -919,7 +914,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596748</v>
+        <v>596739</v>
       </c>
       <c r="R4" t="n">
-        <v>6681394</v>
+        <v>6681387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236580</v>
+        <v>123236581</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1026,7 +1021,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596744</v>
+        <v>596748</v>
       </c>
       <c r="R5" t="n">
-        <v>6681389</v>
+        <v>6681394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236573</v>
+        <v>123236580</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1105,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596831</v>
+        <v>596744</v>
       </c>
       <c r="R6" t="n">
-        <v>6681167</v>
+        <v>6681389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236577</v>
+        <v>123236576</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1247,7 +1247,7 @@
         <v>596739</v>
       </c>
       <c r="R7" t="n">
-        <v>6681387</v>
+        <v>6681388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236575</v>
+        <v>123236577</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596821</v>
+        <v>596739</v>
       </c>
       <c r="R2" t="n">
-        <v>6681191</v>
+        <v>6681387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236573</v>
+        <v>123236575</v>
       </c>
       <c r="B3" t="n">
         <v>97319</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596831</v>
+        <v>596821</v>
       </c>
       <c r="R3" t="n">
-        <v>6681167</v>
+        <v>6681191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236577</v>
+        <v>123236581</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -914,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -923,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596739</v>
+        <v>596748</v>
       </c>
       <c r="R4" t="n">
-        <v>6681387</v>
+        <v>6681394</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236581</v>
+        <v>123236576</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1021,7 +1026,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596748</v>
+        <v>596739</v>
       </c>
       <c r="R5" t="n">
-        <v>6681394</v>
+        <v>6681388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236580</v>
+        <v>123236573</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,42 +1110,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596744</v>
+        <v>596831</v>
       </c>
       <c r="R6" t="n">
-        <v>6681389</v>
+        <v>6681167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1182,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236576</v>
+        <v>123236580</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596739</v>
+        <v>596744</v>
       </c>
       <c r="R7" t="n">
-        <v>6681388</v>
+        <v>6681389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236577</v>
+        <v>123236576</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -722,7 +722,7 @@
         <v>596739</v>
       </c>
       <c r="R2" t="n">
-        <v>6681387</v>
+        <v>6681388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236575</v>
+        <v>123236581</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596821</v>
+        <v>596748</v>
       </c>
       <c r="R3" t="n">
-        <v>6681191</v>
+        <v>6681394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236581</v>
+        <v>123236577</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,7 +924,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596748</v>
+        <v>596739</v>
       </c>
       <c r="R4" t="n">
-        <v>6681394</v>
+        <v>6681387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236576</v>
+        <v>123236573</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,42 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596739</v>
+        <v>596831</v>
       </c>
       <c r="R5" t="n">
-        <v>6681388</v>
+        <v>6681167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1080,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236573</v>
+        <v>123236580</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1110,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596831</v>
+        <v>596744</v>
       </c>
       <c r="R6" t="n">
-        <v>6681167</v>
+        <v>6681389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236580</v>
+        <v>123236575</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,42 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596744</v>
+        <v>596821</v>
       </c>
       <c r="R7" t="n">
-        <v>6681389</v>
+        <v>6681191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1289,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236576</v>
+        <v>123236577</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -722,7 +722,7 @@
         <v>596739</v>
       </c>
       <c r="R2" t="n">
-        <v>6681388</v>
+        <v>6681387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>123236581</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236577</v>
+        <v>123236575</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>97324</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,42 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596739</v>
+        <v>596821</v>
       </c>
       <c r="R4" t="n">
-        <v>6681387</v>
+        <v>6681191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +994,7 @@
         <v>123236573</v>
       </c>
       <c r="B5" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,7 +1096,7 @@
         <v>123236580</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236575</v>
+        <v>123236576</v>
       </c>
       <c r="B7" t="n">
-        <v>97322</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1212,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596821</v>
+        <v>596739</v>
       </c>
       <c r="R7" t="n">
-        <v>6681191</v>
+        <v>6681388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,6 +1288,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236577</v>
+        <v>123236580</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596739</v>
+        <v>596744</v>
       </c>
       <c r="R2" t="n">
-        <v>6681387</v>
+        <v>6681389</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>123236581</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>123236575</v>
       </c>
       <c r="B4" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>123236573</v>
       </c>
       <c r="B5" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236580</v>
+        <v>123236577</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596744</v>
+        <v>596739</v>
       </c>
       <c r="R6" t="n">
-        <v>6681389</v>
+        <v>6681387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
         <v>123236576</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236580</v>
+        <v>123236576</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596744</v>
+        <v>596739</v>
       </c>
       <c r="R2" t="n">
-        <v>6681389</v>
+        <v>6681388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236581</v>
+        <v>123236580</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596748</v>
+        <v>596744</v>
       </c>
       <c r="R3" t="n">
-        <v>6681394</v>
+        <v>6681389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>123236575</v>
       </c>
       <c r="B4" t="n">
-        <v>97330</v>
+        <v>97333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236573</v>
+        <v>123236581</v>
       </c>
       <c r="B5" t="n">
-        <v>97330</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +1003,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596831</v>
+        <v>596748</v>
       </c>
       <c r="R5" t="n">
-        <v>6681167</v>
+        <v>6681394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1079,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236577</v>
+        <v>123236573</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>97333</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,42 +1110,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596739</v>
+        <v>596831</v>
       </c>
       <c r="R6" t="n">
-        <v>6681387</v>
+        <v>6681167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1182,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236576</v>
+        <v>123236577</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1247,7 +1247,7 @@
         <v>596739</v>
       </c>
       <c r="R7" t="n">
-        <v>6681388</v>
+        <v>6681387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236576</v>
+        <v>123236580</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596739</v>
+        <v>596744</v>
       </c>
       <c r="R2" t="n">
-        <v>6681388</v>
+        <v>6681389</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236580</v>
+        <v>123236576</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596744</v>
+        <v>596739</v>
       </c>
       <c r="R3" t="n">
-        <v>6681389</v>
+        <v>6681388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236575</v>
+        <v>123236577</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +901,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596821</v>
+        <v>596739</v>
       </c>
       <c r="R4" t="n">
-        <v>6681191</v>
+        <v>6681387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,7 +999,7 @@
         <v>123236581</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236573</v>
+        <v>123236575</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596831</v>
+        <v>596821</v>
       </c>
       <c r="R6" t="n">
-        <v>6681167</v>
+        <v>6681191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236577</v>
+        <v>123236573</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>97350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,42 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596739</v>
+        <v>596831</v>
       </c>
       <c r="R7" t="n">
-        <v>6681387</v>
+        <v>6681167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1289,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236580</v>
+        <v>123236577</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596744</v>
+        <v>596739</v>
       </c>
       <c r="R2" t="n">
-        <v>6681389</v>
+        <v>6681387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236576</v>
+        <v>123236573</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596739</v>
+        <v>596831</v>
       </c>
       <c r="R3" t="n">
-        <v>6681388</v>
+        <v>6681167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236577</v>
+        <v>123236576</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,7 +931,7 @@
         <v>596739</v>
       </c>
       <c r="R4" t="n">
-        <v>6681387</v>
+        <v>6681388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236581</v>
+        <v>123236580</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,7 +1026,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596748</v>
+        <v>596744</v>
       </c>
       <c r="R5" t="n">
-        <v>6681394</v>
+        <v>6681389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1101,7 @@
         <v>123236575</v>
       </c>
       <c r="B6" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236573</v>
+        <v>123236581</v>
       </c>
       <c r="B7" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1212,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596831</v>
+        <v>596748</v>
       </c>
       <c r="R7" t="n">
-        <v>6681167</v>
+        <v>6681394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,6 +1288,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236577</v>
+        <v>123236581</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596739</v>
+        <v>596748</v>
       </c>
       <c r="R2" t="n">
-        <v>6681387</v>
+        <v>6681394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236573</v>
+        <v>123236580</v>
       </c>
       <c r="B3" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596831</v>
+        <v>596744</v>
       </c>
       <c r="R3" t="n">
-        <v>6681167</v>
+        <v>6681389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236576</v>
+        <v>123236575</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>97369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,42 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596739</v>
+        <v>596821</v>
       </c>
       <c r="R4" t="n">
-        <v>6681388</v>
+        <v>6681191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236580</v>
+        <v>123236576</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596744</v>
+        <v>596739</v>
       </c>
       <c r="R5" t="n">
-        <v>6681389</v>
+        <v>6681388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236575</v>
+        <v>123236577</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1110,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596821</v>
+        <v>596739</v>
       </c>
       <c r="R6" t="n">
-        <v>6681191</v>
+        <v>6681387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236581</v>
+        <v>123236573</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>97369</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,42 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596748</v>
+        <v>596831</v>
       </c>
       <c r="R7" t="n">
-        <v>6681394</v>
+        <v>6681167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1289,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123236581</v>
+        <v>123236576</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596748</v>
+        <v>596739</v>
       </c>
       <c r="R2" t="n">
-        <v>6681394</v>
+        <v>6681388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236580</v>
+        <v>123236581</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596744</v>
+        <v>596748</v>
       </c>
       <c r="R3" t="n">
-        <v>6681389</v>
+        <v>6681394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>123236575</v>
       </c>
       <c r="B4" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236576</v>
+        <v>123236580</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596739</v>
+        <v>596744</v>
       </c>
       <c r="R5" t="n">
-        <v>6681388</v>
+        <v>6681389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
         <v>123236577</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>123236573</v>
       </c>
       <c r="B7" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123236576</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123236581</v>
+        <v>123236577</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,7 +807,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596748</v>
+        <v>596739</v>
       </c>
       <c r="R3" t="n">
-        <v>6681394</v>
+        <v>6681387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,50 +879,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236575</v>
+        <v>123236578</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västermossen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596821</v>
+        <v>596823</v>
       </c>
       <c r="R4" t="n">
-        <v>6681191</v>
+        <v>6681053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +962,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,12 +984,7 @@
         <v>123236580</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236577</v>
+        <v>123236581</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,7 +1113,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596739</v>
+        <v>596748</v>
       </c>
       <c r="R6" t="n">
-        <v>6681387</v>
+        <v>6681394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1188,7 @@
         <v>123236573</v>
       </c>
       <c r="B7" t="n">
-        <v>96957</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,6 +1279,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123236575</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västermossen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596821</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6681191</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10623-2025 artfynd.xlsx
+++ b/artfynd/A 10623-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236576</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236577</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236578</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236580</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236573</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,8 +1411,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236575</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>